--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-08-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-08-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6177678d5+2802741]
-	GetHandleVerifier [0x0x7ff6174ceb70+79568]
-	(No symbol) [0x0x7ff61726c0fa]
-	(No symbol) [0x0x7ff6172c2a96]
-	(No symbol) [0x0x7ff6172c2d4c]
-	(No symbol) [0x0x7ff617316017]
-	(No symbol) [0x0x7ff6172eaccf]
-	(No symbol) [0x0x7ff617312e24]
-	(No symbol) [0x0x7ff6172eaa63]
-	(No symbol) [0x0x7ff6172b3c91]
-	(No symbol) [0x0x7ff6172b4a23]
-	GetHandleVerifier [0x0x7ff617792ced+2979917]
-	GetHandleVerifier [0x0x7ff61778d0f3+2956371]
-	GetHandleVerifier [0x0x7ff6177aacbd+3078173]
-	GetHandleVerifier [0x0x7ff6174e836e+184014]
-	GetHandleVerifier [0x0x7ff6174f024f+216495]
-	GetHandleVerifier [0x0x7ff6174d70c4+113700]
-	GetHandleVerifier [0x0x7ff6174d7279+114137]
-	GetHandleVerifier [0x0x7ff6174bdf78+10968]
+	GetHandleVerifier [0x0x7ff7693778d5+2802741]
+	GetHandleVerifier [0x0x7ff7690deb70+79568]
+	(No symbol) [0x0x7ff768e7c0fa]
+	(No symbol) [0x0x7ff768ed2a96]
+	(No symbol) [0x0x7ff768ed2d4c]
+	(No symbol) [0x0x7ff768f26017]
+	(No symbol) [0x0x7ff768efaccf]
+	(No symbol) [0x0x7ff768f22e24]
+	(No symbol) [0x0x7ff768efaa63]
+	(No symbol) [0x0x7ff768ec3c91]
+	(No symbol) [0x0x7ff768ec4a23]
+	GetHandleVerifier [0x0x7ff7693a2ced+2979917]
+	GetHandleVerifier [0x0x7ff76939d0f3+2956371]
+	GetHandleVerifier [0x0x7ff7693bacbd+3078173]
+	GetHandleVerifier [0x0x7ff7690f836e+184014]
+	GetHandleVerifier [0x0x7ff76910024f+216495]
+	GetHandleVerifier [0x0x7ff7690e70c4+113700]
+	GetHandleVerifier [0x0x7ff7690e7279+114137]
+	GetHandleVerifier [0x0x7ff7690cdf78+10968]
 	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
 	RtlUserThreadStart [0x0x7fffa3edc34c+44]
 </t>
